--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34682-2026 artfynd.xlsx
+++ b/artfynd/A 34682-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136666890</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136666887</v>
       </c>
       <c r="B3" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136666888</v>
       </c>
       <c r="B4" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
